--- a/signal_tracker.xlsx
+++ b/signal_tracker.xlsx
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K2"/>
+  <dimension ref="A1:K3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -525,6 +525,47 @@
       </c>
       <c r="K2" t="n">
         <v>475.3703324368939</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>2026-09-15 09:15:51</t>
+        </is>
+      </c>
+      <c r="B3" t="n">
+        <v>75156.48</v>
+      </c>
+      <c r="C3" t="n">
+        <v>12.34</v>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>SENSEX2691775100CE</t>
+        </is>
+      </c>
+      <c r="E3" t="n">
+        <v>407.5</v>
+      </c>
+      <c r="F3" t="n">
+        <v>334.5958926087085</v>
+      </c>
+      <c r="G3" t="n">
+        <v>480.4041073912915</v>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>SENSEX2691775200PE</t>
+        </is>
+      </c>
+      <c r="I3" t="n">
+        <v>360</v>
+      </c>
+      <c r="J3" t="n">
+        <v>313.2745804436913</v>
+      </c>
+      <c r="K3" t="n">
+        <v>406.7254195563087</v>
       </c>
     </row>
   </sheetData>

--- a/signal_tracker.xlsx
+++ b/signal_tracker.xlsx
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K3"/>
+  <dimension ref="A1:K4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -566,6 +566,47 @@
       </c>
       <c r="K3" t="n">
         <v>406.7254195563087</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>2026-09-15 15:35:43</t>
+        </is>
+      </c>
+      <c r="B4" t="n">
+        <v>74003.82000000001</v>
+      </c>
+      <c r="C4" t="n">
+        <v>13.46</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>SENSEX2691774000CE</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>400</v>
+      </c>
+      <c r="F4" t="n">
+        <v>330.595000804583</v>
+      </c>
+      <c r="G4" t="n">
+        <v>469.404999195417</v>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>SENSEX2691774100PE</t>
+        </is>
+      </c>
+      <c r="I4" t="n">
+        <v>379.9</v>
+      </c>
+      <c r="J4" t="n">
+        <v>317.7038035499912</v>
+      </c>
+      <c r="K4" t="n">
+        <v>442.0961964500088</v>
       </c>
     </row>
   </sheetData>

--- a/signal_tracker.xlsx
+++ b/signal_tracker.xlsx
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K4"/>
+  <dimension ref="A1:K5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -607,6 +607,47 @@
       </c>
       <c r="K4" t="n">
         <v>442.0961964500088</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>2026-09-16 13:40:31</t>
+        </is>
+      </c>
+      <c r="B5" t="n">
+        <v>74295.11</v>
+      </c>
+      <c r="C5" t="n">
+        <v>13.2</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>SENSEX2691774200CE</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>352</v>
+      </c>
+      <c r="F5" t="n">
+        <v>312.9122903003016</v>
+      </c>
+      <c r="G5" t="n">
+        <v>391.0877096996984</v>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>SENSEX2691774400PE</t>
+        </is>
+      </c>
+      <c r="I5" t="n">
+        <v>384</v>
+      </c>
+      <c r="J5" t="n">
+        <v>346.0520021721514</v>
+      </c>
+      <c r="K5" t="n">
+        <v>421.9479978278486</v>
       </c>
     </row>
   </sheetData>
@@ -620,9 +661,171 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A1"/>
+  <dimension ref="A1:G5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <sheetData/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>timestamp</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>mode</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>state</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>trading_symbol</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>price</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>qty</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>trades_count</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>2026-09-16 14:00:36</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>LIVE</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>ENTRY</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>SENSEX2691774400PE</t>
+        </is>
+      </c>
+      <c r="E2" t="n">
+        <v>370.65</v>
+      </c>
+      <c r="F2" t="n">
+        <v>40</v>
+      </c>
+      <c r="G2" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>2026-09-16 14:00:41</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>LIVE</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>MANUAL_EXIT</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>SENSEX2691774400PE</t>
+        </is>
+      </c>
+      <c r="E3" t="n">
+        <v>358.55</v>
+      </c>
+      <c r="F3" t="n">
+        <v>40</v>
+      </c>
+      <c r="G3" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>2026-09-16 14:08:03</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>LIVE</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>ENTRY</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>SENSEX2691774400PE</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>360.6</v>
+      </c>
+      <c r="F4" t="n">
+        <v>40</v>
+      </c>
+      <c r="G4" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>2026-09-16 14:08:08</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>LIVE</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>MANUAL_EXIT</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>SENSEX2691774400PE</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>360.4</v>
+      </c>
+      <c r="F5" t="n">
+        <v>40</v>
+      </c>
+      <c r="G5" t="n">
+        <v>2</v>
+      </c>
+    </row>
+  </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/signal_tracker.xlsx
+++ b/signal_tracker.xlsx
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K5"/>
+  <dimension ref="A1:U6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -485,6 +485,56 @@
           <t>pe_upper</t>
         </is>
       </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>mode</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>signal_name</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>entry_reason</t>
+        </is>
+      </c>
+      <c r="O1" s="1" t="inlineStr">
+        <is>
+          <t>trading_symbol</t>
+        </is>
+      </c>
+      <c r="P1" s="1" t="inlineStr">
+        <is>
+          <t>entry_price</t>
+        </is>
+      </c>
+      <c r="Q1" s="1" t="inlineStr">
+        <is>
+          <t>exit_reason</t>
+        </is>
+      </c>
+      <c r="R1" s="1" t="inlineStr">
+        <is>
+          <t>exit_price</t>
+        </is>
+      </c>
+      <c r="S1" s="1" t="inlineStr">
+        <is>
+          <t>pnl_pts</t>
+        </is>
+      </c>
+      <c r="T1" s="1" t="inlineStr">
+        <is>
+          <t>pnl_amount</t>
+        </is>
+      </c>
+      <c r="U1" s="1" t="inlineStr">
+        <is>
+          <t>status</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -526,6 +576,16 @@
       <c r="K2" t="n">
         <v>475.3703324368939</v>
       </c>
+      <c r="L2" t="inlineStr"/>
+      <c r="M2" t="inlineStr"/>
+      <c r="N2" t="inlineStr"/>
+      <c r="O2" t="inlineStr"/>
+      <c r="P2" t="inlineStr"/>
+      <c r="Q2" t="inlineStr"/>
+      <c r="R2" t="inlineStr"/>
+      <c r="S2" t="inlineStr"/>
+      <c r="T2" t="inlineStr"/>
+      <c r="U2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -567,6 +627,16 @@
       <c r="K3" t="n">
         <v>406.7254195563087</v>
       </c>
+      <c r="L3" t="inlineStr"/>
+      <c r="M3" t="inlineStr"/>
+      <c r="N3" t="inlineStr"/>
+      <c r="O3" t="inlineStr"/>
+      <c r="P3" t="inlineStr"/>
+      <c r="Q3" t="inlineStr"/>
+      <c r="R3" t="inlineStr"/>
+      <c r="S3" t="inlineStr"/>
+      <c r="T3" t="inlineStr"/>
+      <c r="U3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -608,6 +678,16 @@
       <c r="K4" t="n">
         <v>442.0961964500088</v>
       </c>
+      <c r="L4" t="inlineStr"/>
+      <c r="M4" t="inlineStr"/>
+      <c r="N4" t="inlineStr"/>
+      <c r="O4" t="inlineStr"/>
+      <c r="P4" t="inlineStr"/>
+      <c r="Q4" t="inlineStr"/>
+      <c r="R4" t="inlineStr"/>
+      <c r="S4" t="inlineStr"/>
+      <c r="T4" t="inlineStr"/>
+      <c r="U4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -648,6 +728,75 @@
       </c>
       <c r="K5" t="n">
         <v>421.9479978278486</v>
+      </c>
+      <c r="L5" t="inlineStr"/>
+      <c r="M5" t="inlineStr"/>
+      <c r="N5" t="inlineStr"/>
+      <c r="O5" t="inlineStr"/>
+      <c r="P5" t="inlineStr"/>
+      <c r="Q5" t="inlineStr"/>
+      <c r="R5" t="inlineStr"/>
+      <c r="S5" t="inlineStr"/>
+      <c r="T5" t="inlineStr"/>
+      <c r="U5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>2026-09-16 14:19:31</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr"/>
+      <c r="C6" t="inlineStr"/>
+      <c r="D6" t="inlineStr"/>
+      <c r="E6" t="inlineStr"/>
+      <c r="F6" t="inlineStr"/>
+      <c r="G6" t="inlineStr"/>
+      <c r="H6" t="inlineStr"/>
+      <c r="I6" t="inlineStr"/>
+      <c r="J6" t="inlineStr"/>
+      <c r="K6" t="inlineStr"/>
+      <c r="L6" t="inlineStr">
+        <is>
+          <t>LIVE</t>
+        </is>
+      </c>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>Wick Absorption &amp; Multi-TF Confluence Breakout Entry</t>
+        </is>
+      </c>
+      <c r="N6" t="inlineStr">
+        <is>
+          <t>PE Wick Absorption &amp; Multi-TF Confluence Breakout Entry (Score: 30/100, Wick: 83.6%)</t>
+        </is>
+      </c>
+      <c r="O6" t="inlineStr">
+        <is>
+          <t>SENSEX2691774400PE</t>
+        </is>
+      </c>
+      <c r="P6" t="n">
+        <v>331.65</v>
+      </c>
+      <c r="Q6" t="inlineStr">
+        <is>
+          <t>SIGNAL_ALERT_ONLY</t>
+        </is>
+      </c>
+      <c r="R6" t="n">
+        <v>331.65</v>
+      </c>
+      <c r="S6" t="n">
+        <v>0</v>
+      </c>
+      <c r="T6" t="n">
+        <v>0</v>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>ALERT_ONLY_NO_TRADE</t>
+        </is>
       </c>
     </row>
   </sheetData>
@@ -661,7 +810,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G5"/>
+  <dimension ref="A1:G9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -825,6 +974,130 @@
         <v>2</v>
       </c>
     </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>2026-09-16 14:16:07</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>PAPER</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>ENTRY</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>SENSEX2691774400PE</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>340.55</v>
+      </c>
+      <c r="F6" t="n">
+        <v>40</v>
+      </c>
+      <c r="G6" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>2026-09-16 14:19:11</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>LIVE</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>MANUAL_EXIT</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>SENSEX2691774400PE</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>331.65</v>
+      </c>
+      <c r="F7" t="n">
+        <v>80</v>
+      </c>
+      <c r="G7" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>2026-09-16 14:20:18</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>LIVE</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>ENTRY</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>SENSEX2691774400PE</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>350.95</v>
+      </c>
+      <c r="F8" t="n">
+        <v>40</v>
+      </c>
+      <c r="G8" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>2026-09-16 14:20:23</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>LIVE</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>MANUAL_EXIT</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>SENSEX2691774400PE</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>347.05</v>
+      </c>
+      <c r="F9" t="n">
+        <v>40</v>
+      </c>
+      <c r="G9" t="n">
+        <v>2</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/signal_tracker.xlsx
+++ b/signal_tracker.xlsx
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:U6"/>
+  <dimension ref="A1:U8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -798,6 +798,108 @@
           <t>ALERT_ONLY_NO_TRADE</t>
         </is>
       </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>2026-09-17 09:16:59</t>
+        </is>
+      </c>
+      <c r="B7" t="n">
+        <v>74259.61</v>
+      </c>
+      <c r="C7" t="n">
+        <v>12.9</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>SENSEX2691774200CE</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>247.4</v>
+      </c>
+      <c r="F7" t="n">
+        <v>220.8967365955033</v>
+      </c>
+      <c r="G7" t="n">
+        <v>273.9032634044967</v>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>SENSEX2691774400PE</t>
+        </is>
+      </c>
+      <c r="I7" t="n">
+        <v>355.45</v>
+      </c>
+      <c r="J7" t="n">
+        <v>325.7299308328091</v>
+      </c>
+      <c r="K7" t="n">
+        <v>385.1700691671908</v>
+      </c>
+      <c r="L7" t="inlineStr"/>
+      <c r="M7" t="inlineStr"/>
+      <c r="N7" t="inlineStr"/>
+      <c r="O7" t="inlineStr"/>
+      <c r="P7" t="inlineStr"/>
+      <c r="Q7" t="inlineStr"/>
+      <c r="R7" t="inlineStr"/>
+      <c r="S7" t="inlineStr"/>
+      <c r="T7" t="inlineStr"/>
+      <c r="U7" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>2026-09-17 09:45:42</t>
+        </is>
+      </c>
+      <c r="B8" t="n">
+        <v>74390.3</v>
+      </c>
+      <c r="C8" t="n">
+        <v>12.71</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>SENSEX2691774300CE</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>245.9</v>
+      </c>
+      <c r="F8" t="n">
+        <v>218.1211544517704</v>
+      </c>
+      <c r="G8" t="n">
+        <v>273.6788455482296</v>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>SENSEX2691774500PE</t>
+        </is>
+      </c>
+      <c r="I8" t="n">
+        <v>264.4</v>
+      </c>
+      <c r="J8" t="n">
+        <v>236.4542897841182</v>
+      </c>
+      <c r="K8" t="n">
+        <v>292.3457102158818</v>
+      </c>
+      <c r="L8" t="inlineStr"/>
+      <c r="M8" t="inlineStr"/>
+      <c r="N8" t="inlineStr"/>
+      <c r="O8" t="inlineStr"/>
+      <c r="P8" t="inlineStr"/>
+      <c r="Q8" t="inlineStr"/>
+      <c r="R8" t="inlineStr"/>
+      <c r="S8" t="inlineStr"/>
+      <c r="T8" t="inlineStr"/>
+      <c r="U8" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/signal_tracker.xlsx
+++ b/signal_tracker.xlsx
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:U8"/>
+  <dimension ref="A1:Y10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -533,6 +533,26 @@
       <c r="U1" s="1" t="inlineStr">
         <is>
           <t>status</t>
+        </is>
+      </c>
+      <c r="V1" s="1" t="inlineStr">
+        <is>
+          <t>state</t>
+        </is>
+      </c>
+      <c r="W1" s="1" t="inlineStr">
+        <is>
+          <t>qty</t>
+        </is>
+      </c>
+      <c r="X1" s="1" t="inlineStr">
+        <is>
+          <t>result</t>
+        </is>
+      </c>
+      <c r="Y1" s="1" t="inlineStr">
+        <is>
+          <t>trades_count</t>
         </is>
       </c>
     </row>
@@ -586,6 +606,10 @@
       <c r="S2" t="inlineStr"/>
       <c r="T2" t="inlineStr"/>
       <c r="U2" t="inlineStr"/>
+      <c r="V2" t="inlineStr"/>
+      <c r="W2" t="inlineStr"/>
+      <c r="X2" t="inlineStr"/>
+      <c r="Y2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -637,6 +661,10 @@
       <c r="S3" t="inlineStr"/>
       <c r="T3" t="inlineStr"/>
       <c r="U3" t="inlineStr"/>
+      <c r="V3" t="inlineStr"/>
+      <c r="W3" t="inlineStr"/>
+      <c r="X3" t="inlineStr"/>
+      <c r="Y3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -688,6 +716,10 @@
       <c r="S4" t="inlineStr"/>
       <c r="T4" t="inlineStr"/>
       <c r="U4" t="inlineStr"/>
+      <c r="V4" t="inlineStr"/>
+      <c r="W4" t="inlineStr"/>
+      <c r="X4" t="inlineStr"/>
+      <c r="Y4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -739,6 +771,10 @@
       <c r="S5" t="inlineStr"/>
       <c r="T5" t="inlineStr"/>
       <c r="U5" t="inlineStr"/>
+      <c r="V5" t="inlineStr"/>
+      <c r="W5" t="inlineStr"/>
+      <c r="X5" t="inlineStr"/>
+      <c r="Y5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -798,6 +834,10 @@
           <t>ALERT_ONLY_NO_TRADE</t>
         </is>
       </c>
+      <c r="V6" t="inlineStr"/>
+      <c r="W6" t="inlineStr"/>
+      <c r="X6" t="inlineStr"/>
+      <c r="Y6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -849,6 +889,10 @@
       <c r="S7" t="inlineStr"/>
       <c r="T7" t="inlineStr"/>
       <c r="U7" t="inlineStr"/>
+      <c r="V7" t="inlineStr"/>
+      <c r="W7" t="inlineStr"/>
+      <c r="X7" t="inlineStr"/>
+      <c r="Y7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -900,6 +944,136 @@
       <c r="S8" t="inlineStr"/>
       <c r="T8" t="inlineStr"/>
       <c r="U8" t="inlineStr"/>
+      <c r="V8" t="inlineStr"/>
+      <c r="W8" t="inlineStr"/>
+      <c r="X8" t="inlineStr"/>
+      <c r="Y8" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>2026-09-17 12:41:25</t>
+        </is>
+      </c>
+      <c r="B9" t="n">
+        <v>74646.00999999999</v>
+      </c>
+      <c r="C9" t="n">
+        <v>12.29</v>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>SENSEX2691774500CE</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>252.1</v>
+      </c>
+      <c r="F9" t="n">
+        <v>222.3044551200572</v>
+      </c>
+      <c r="G9" t="n">
+        <v>281.8955448799428</v>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>SENSEX2691774700PE</t>
+        </is>
+      </c>
+      <c r="I9" t="n">
+        <v>194.7</v>
+      </c>
+      <c r="J9" t="n">
+        <v>170.2491163676127</v>
+      </c>
+      <c r="K9" t="n">
+        <v>219.1508836323873</v>
+      </c>
+      <c r="L9" t="inlineStr"/>
+      <c r="M9" t="inlineStr"/>
+      <c r="N9" t="inlineStr"/>
+      <c r="O9" t="inlineStr"/>
+      <c r="P9" t="inlineStr"/>
+      <c r="Q9" t="inlineStr"/>
+      <c r="R9" t="inlineStr"/>
+      <c r="S9" t="inlineStr"/>
+      <c r="T9" t="inlineStr"/>
+      <c r="U9" t="inlineStr"/>
+      <c r="V9" t="inlineStr"/>
+      <c r="W9" t="inlineStr"/>
+      <c r="X9" t="inlineStr"/>
+      <c r="Y9" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>2026-09-17 12:44:25</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr"/>
+      <c r="C10" t="inlineStr"/>
+      <c r="D10" t="inlineStr"/>
+      <c r="E10" t="inlineStr"/>
+      <c r="F10" t="inlineStr"/>
+      <c r="G10" t="inlineStr"/>
+      <c r="H10" t="inlineStr"/>
+      <c r="I10" t="inlineStr"/>
+      <c r="J10" t="inlineStr"/>
+      <c r="K10" t="inlineStr"/>
+      <c r="L10" t="inlineStr">
+        <is>
+          <t>PAPER</t>
+        </is>
+      </c>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>Dynamic EPM Low Bounce LONG Entry</t>
+        </is>
+      </c>
+      <c r="N10" t="inlineStr">
+        <is>
+          <t>CE Dynamic EPM Low Bounce LONG Entry (Score: 100/100, Wick: 48.3%, EPM Low: ₹222.30 | SL-18.0)</t>
+        </is>
+      </c>
+      <c r="O10" t="inlineStr">
+        <is>
+          <t>SENSEX2691774500CE</t>
+        </is>
+      </c>
+      <c r="P10" t="n">
+        <v>252.3</v>
+      </c>
+      <c r="Q10" t="inlineStr">
+        <is>
+          <t>STOP LOSS HIT</t>
+        </is>
+      </c>
+      <c r="R10" t="n">
+        <v>231.6</v>
+      </c>
+      <c r="S10" t="n">
+        <v>-20.7</v>
+      </c>
+      <c r="T10" t="n">
+        <v>-828</v>
+      </c>
+      <c r="U10" t="inlineStr"/>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>EXIT_SL</t>
+        </is>
+      </c>
+      <c r="W10" t="n">
+        <v>40</v>
+      </c>
+      <c r="X10" t="inlineStr">
+        <is>
+          <t>LOSS</t>
+        </is>
+      </c>
+      <c r="Y10" t="n">
+        <v>1</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -912,7 +1086,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G9"/>
+  <dimension ref="A1:O17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -951,6 +1125,46 @@
           <t>trades_count</t>
         </is>
       </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>signal_name</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>entry_reason</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>exit_reason</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>entry_price</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>exit_price</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>pnl_pts</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>pnl_amount</t>
+        </is>
+      </c>
+      <c r="O1" s="1" t="inlineStr">
+        <is>
+          <t>result</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -982,6 +1196,14 @@
       <c r="G2" t="n">
         <v>1</v>
       </c>
+      <c r="H2" t="inlineStr"/>
+      <c r="I2" t="inlineStr"/>
+      <c r="J2" t="inlineStr"/>
+      <c r="K2" t="inlineStr"/>
+      <c r="L2" t="inlineStr"/>
+      <c r="M2" t="inlineStr"/>
+      <c r="N2" t="inlineStr"/>
+      <c r="O2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -1013,6 +1235,14 @@
       <c r="G3" t="n">
         <v>1</v>
       </c>
+      <c r="H3" t="inlineStr"/>
+      <c r="I3" t="inlineStr"/>
+      <c r="J3" t="inlineStr"/>
+      <c r="K3" t="inlineStr"/>
+      <c r="L3" t="inlineStr"/>
+      <c r="M3" t="inlineStr"/>
+      <c r="N3" t="inlineStr"/>
+      <c r="O3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -1044,6 +1274,14 @@
       <c r="G4" t="n">
         <v>2</v>
       </c>
+      <c r="H4" t="inlineStr"/>
+      <c r="I4" t="inlineStr"/>
+      <c r="J4" t="inlineStr"/>
+      <c r="K4" t="inlineStr"/>
+      <c r="L4" t="inlineStr"/>
+      <c r="M4" t="inlineStr"/>
+      <c r="N4" t="inlineStr"/>
+      <c r="O4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -1075,6 +1313,14 @@
       <c r="G5" t="n">
         <v>2</v>
       </c>
+      <c r="H5" t="inlineStr"/>
+      <c r="I5" t="inlineStr"/>
+      <c r="J5" t="inlineStr"/>
+      <c r="K5" t="inlineStr"/>
+      <c r="L5" t="inlineStr"/>
+      <c r="M5" t="inlineStr"/>
+      <c r="N5" t="inlineStr"/>
+      <c r="O5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -1106,6 +1352,14 @@
       <c r="G6" t="n">
         <v>1</v>
       </c>
+      <c r="H6" t="inlineStr"/>
+      <c r="I6" t="inlineStr"/>
+      <c r="J6" t="inlineStr"/>
+      <c r="K6" t="inlineStr"/>
+      <c r="L6" t="inlineStr"/>
+      <c r="M6" t="inlineStr"/>
+      <c r="N6" t="inlineStr"/>
+      <c r="O6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -1137,6 +1391,14 @@
       <c r="G7" t="n">
         <v>1</v>
       </c>
+      <c r="H7" t="inlineStr"/>
+      <c r="I7" t="inlineStr"/>
+      <c r="J7" t="inlineStr"/>
+      <c r="K7" t="inlineStr"/>
+      <c r="L7" t="inlineStr"/>
+      <c r="M7" t="inlineStr"/>
+      <c r="N7" t="inlineStr"/>
+      <c r="O7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -1168,6 +1430,14 @@
       <c r="G8" t="n">
         <v>2</v>
       </c>
+      <c r="H8" t="inlineStr"/>
+      <c r="I8" t="inlineStr"/>
+      <c r="J8" t="inlineStr"/>
+      <c r="K8" t="inlineStr"/>
+      <c r="L8" t="inlineStr"/>
+      <c r="M8" t="inlineStr"/>
+      <c r="N8" t="inlineStr"/>
+      <c r="O8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -1199,6 +1469,348 @@
       <c r="G9" t="n">
         <v>2</v>
       </c>
+      <c r="H9" t="inlineStr"/>
+      <c r="I9" t="inlineStr"/>
+      <c r="J9" t="inlineStr"/>
+      <c r="K9" t="inlineStr"/>
+      <c r="L9" t="inlineStr"/>
+      <c r="M9" t="inlineStr"/>
+      <c r="N9" t="inlineStr"/>
+      <c r="O9" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>2026-09-17 12:42:04</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>PAPER</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>ENTRY</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>SENSEX2691774500CE</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>252.3</v>
+      </c>
+      <c r="F10" t="n">
+        <v>40</v>
+      </c>
+      <c r="G10" t="n">
+        <v>1</v>
+      </c>
+      <c r="H10" t="inlineStr"/>
+      <c r="I10" t="inlineStr"/>
+      <c r="J10" t="inlineStr"/>
+      <c r="K10" t="inlineStr"/>
+      <c r="L10" t="inlineStr"/>
+      <c r="M10" t="inlineStr"/>
+      <c r="N10" t="inlineStr"/>
+      <c r="O10" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>2026-09-17 12:44:25</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>PAPER</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>EXIT_SL</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>SENSEX2691774500CE</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr"/>
+      <c r="F11" t="n">
+        <v>40</v>
+      </c>
+      <c r="G11" t="n">
+        <v>1</v>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>Dynamic EPM Low Bounce LONG Entry</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>CE Dynamic EPM Low Bounce LONG Entry (Score: 100/100, Wick: 48.3%, EPM Low: ₹222.30 | SL-18.0)</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>STOP LOSS HIT</t>
+        </is>
+      </c>
+      <c r="K11" t="n">
+        <v>252.3</v>
+      </c>
+      <c r="L11" t="n">
+        <v>231.6</v>
+      </c>
+      <c r="M11" t="n">
+        <v>-20.7</v>
+      </c>
+      <c r="N11" t="n">
+        <v>-828</v>
+      </c>
+      <c r="O11" t="inlineStr">
+        <is>
+          <t>LOSS</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>2026-09-17 12:45:25</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>PAPER</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>ENTRY</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>SENSEX2691774700PE</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>220.4</v>
+      </c>
+      <c r="F12" t="n">
+        <v>40</v>
+      </c>
+      <c r="G12" t="n">
+        <v>2</v>
+      </c>
+      <c r="H12" t="inlineStr"/>
+      <c r="I12" t="inlineStr"/>
+      <c r="J12" t="inlineStr"/>
+      <c r="K12" t="inlineStr"/>
+      <c r="L12" t="inlineStr"/>
+      <c r="M12" t="inlineStr"/>
+      <c r="N12" t="inlineStr"/>
+      <c r="O12" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>2026-09-17 12:49:19</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>LIVE</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>MANUAL_EXIT</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>SENSEX2691774700PE</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>239.3</v>
+      </c>
+      <c r="F13" t="n">
+        <v>40</v>
+      </c>
+      <c r="G13" t="n">
+        <v>2</v>
+      </c>
+      <c r="H13" t="inlineStr"/>
+      <c r="I13" t="inlineStr"/>
+      <c r="J13" t="inlineStr"/>
+      <c r="K13" t="inlineStr"/>
+      <c r="L13" t="inlineStr"/>
+      <c r="M13" t="inlineStr"/>
+      <c r="N13" t="inlineStr"/>
+      <c r="O13" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>2026-09-17 12:51:30</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>LIVE</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>ENTRY</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>SENSEX2691774700PE</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>232.95</v>
+      </c>
+      <c r="F14" t="n">
+        <v>40</v>
+      </c>
+      <c r="G14" t="n">
+        <v>3</v>
+      </c>
+      <c r="H14" t="inlineStr"/>
+      <c r="I14" t="inlineStr"/>
+      <c r="J14" t="inlineStr"/>
+      <c r="K14" t="inlineStr"/>
+      <c r="L14" t="inlineStr"/>
+      <c r="M14" t="inlineStr"/>
+      <c r="N14" t="inlineStr"/>
+      <c r="O14" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>2026-09-17 12:51:34</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>LIVE</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>MANUAL_EXIT</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>SENSEX2691774700PE</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>231.1</v>
+      </c>
+      <c r="F15" t="n">
+        <v>40</v>
+      </c>
+      <c r="G15" t="n">
+        <v>3</v>
+      </c>
+      <c r="H15" t="inlineStr"/>
+      <c r="I15" t="inlineStr"/>
+      <c r="J15" t="inlineStr"/>
+      <c r="K15" t="inlineStr"/>
+      <c r="L15" t="inlineStr"/>
+      <c r="M15" t="inlineStr"/>
+      <c r="N15" t="inlineStr"/>
+      <c r="O15" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>2026-09-17 12:53:13</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>LIVE</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>ENTRY</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>SENSEX2691774700PE</t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>236.9</v>
+      </c>
+      <c r="F16" t="n">
+        <v>40</v>
+      </c>
+      <c r="G16" t="n">
+        <v>4</v>
+      </c>
+      <c r="H16" t="inlineStr"/>
+      <c r="I16" t="inlineStr"/>
+      <c r="J16" t="inlineStr"/>
+      <c r="K16" t="inlineStr"/>
+      <c r="L16" t="inlineStr"/>
+      <c r="M16" t="inlineStr"/>
+      <c r="N16" t="inlineStr"/>
+      <c r="O16" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>2026-09-17 12:53:18</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>LIVE</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>MANUAL_EXIT</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>SENSEX2691774700PE</t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>232.1</v>
+      </c>
+      <c r="F17" t="n">
+        <v>40</v>
+      </c>
+      <c r="G17" t="n">
+        <v>4</v>
+      </c>
+      <c r="H17" t="inlineStr"/>
+      <c r="I17" t="inlineStr"/>
+      <c r="J17" t="inlineStr"/>
+      <c r="K17" t="inlineStr"/>
+      <c r="L17" t="inlineStr"/>
+      <c r="M17" t="inlineStr"/>
+      <c r="N17" t="inlineStr"/>
+      <c r="O17" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/signal_tracker.xlsx
+++ b/signal_tracker.xlsx
@@ -1086,7 +1086,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O17"/>
+  <dimension ref="A1:O33"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1812,6 +1812,630 @@
       <c r="N17" t="inlineStr"/>
       <c r="O17" t="inlineStr"/>
     </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>2026-09-17 14:15:36</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>LIVE</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>ENTRY</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>SENSEX2691774500CE</t>
+        </is>
+      </c>
+      <c r="E18" t="n">
+        <v>109.2</v>
+      </c>
+      <c r="F18" t="n">
+        <v>40</v>
+      </c>
+      <c r="G18" t="n">
+        <v>1</v>
+      </c>
+      <c r="H18" t="inlineStr"/>
+      <c r="I18" t="inlineStr"/>
+      <c r="J18" t="inlineStr"/>
+      <c r="K18" t="inlineStr"/>
+      <c r="L18" t="inlineStr"/>
+      <c r="M18" t="inlineStr"/>
+      <c r="N18" t="inlineStr"/>
+      <c r="O18" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>2026-09-17 14:15:40</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>LIVE</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>MANUAL_EXIT</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>SENSEX2691774500CE</t>
+        </is>
+      </c>
+      <c r="E19" t="n">
+        <v>106.9</v>
+      </c>
+      <c r="F19" t="n">
+        <v>40</v>
+      </c>
+      <c r="G19" t="n">
+        <v>1</v>
+      </c>
+      <c r="H19" t="inlineStr"/>
+      <c r="I19" t="inlineStr"/>
+      <c r="J19" t="inlineStr"/>
+      <c r="K19" t="inlineStr"/>
+      <c r="L19" t="inlineStr"/>
+      <c r="M19" t="inlineStr"/>
+      <c r="N19" t="inlineStr"/>
+      <c r="O19" t="inlineStr"/>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>2026-09-17 14:16:18</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>LIVE</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>ENTRY</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>SENSEX2691774500CE</t>
+        </is>
+      </c>
+      <c r="E20" t="n">
+        <v>106.9</v>
+      </c>
+      <c r="F20" t="n">
+        <v>40</v>
+      </c>
+      <c r="G20" t="n">
+        <v>2</v>
+      </c>
+      <c r="H20" t="inlineStr"/>
+      <c r="I20" t="inlineStr"/>
+      <c r="J20" t="inlineStr"/>
+      <c r="K20" t="inlineStr"/>
+      <c r="L20" t="inlineStr"/>
+      <c r="M20" t="inlineStr"/>
+      <c r="N20" t="inlineStr"/>
+      <c r="O20" t="inlineStr"/>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>2026-09-17 14:16:22</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>LIVE</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>MANUAL_EXIT</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>SENSEX2691774500CE</t>
+        </is>
+      </c>
+      <c r="E21" t="n">
+        <v>103.6</v>
+      </c>
+      <c r="F21" t="n">
+        <v>40</v>
+      </c>
+      <c r="G21" t="n">
+        <v>2</v>
+      </c>
+      <c r="H21" t="inlineStr"/>
+      <c r="I21" t="inlineStr"/>
+      <c r="J21" t="inlineStr"/>
+      <c r="K21" t="inlineStr"/>
+      <c r="L21" t="inlineStr"/>
+      <c r="M21" t="inlineStr"/>
+      <c r="N21" t="inlineStr"/>
+      <c r="O21" t="inlineStr"/>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>2026-09-17 14:20:46</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>LIVE</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>ENTRY</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>SENSEX2691774500CE</t>
+        </is>
+      </c>
+      <c r="E22" t="n">
+        <v>112.2</v>
+      </c>
+      <c r="F22" t="n">
+        <v>40</v>
+      </c>
+      <c r="G22" t="n">
+        <v>3</v>
+      </c>
+      <c r="H22" t="inlineStr"/>
+      <c r="I22" t="inlineStr"/>
+      <c r="J22" t="inlineStr"/>
+      <c r="K22" t="inlineStr"/>
+      <c r="L22" t="inlineStr"/>
+      <c r="M22" t="inlineStr"/>
+      <c r="N22" t="inlineStr"/>
+      <c r="O22" t="inlineStr"/>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>2026-09-17 14:20:50</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>LIVE</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>MANUAL_EXIT</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>SENSEX2691774500CE</t>
+        </is>
+      </c>
+      <c r="E23" t="n">
+        <v>117.8</v>
+      </c>
+      <c r="F23" t="n">
+        <v>40</v>
+      </c>
+      <c r="G23" t="n">
+        <v>3</v>
+      </c>
+      <c r="H23" t="inlineStr"/>
+      <c r="I23" t="inlineStr"/>
+      <c r="J23" t="inlineStr"/>
+      <c r="K23" t="inlineStr"/>
+      <c r="L23" t="inlineStr"/>
+      <c r="M23" t="inlineStr"/>
+      <c r="N23" t="inlineStr"/>
+      <c r="O23" t="inlineStr"/>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>2026-09-17 14:30:59</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>LIVE</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>ENTRY</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>SENSEX2691774500CE</t>
+        </is>
+      </c>
+      <c r="E24" t="n">
+        <v>116.45</v>
+      </c>
+      <c r="F24" t="n">
+        <v>40</v>
+      </c>
+      <c r="G24" t="n">
+        <v>4</v>
+      </c>
+      <c r="H24" t="inlineStr"/>
+      <c r="I24" t="inlineStr"/>
+      <c r="J24" t="inlineStr"/>
+      <c r="K24" t="inlineStr"/>
+      <c r="L24" t="inlineStr"/>
+      <c r="M24" t="inlineStr"/>
+      <c r="N24" t="inlineStr"/>
+      <c r="O24" t="inlineStr"/>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>2026-09-17 14:31:04</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>LIVE</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>MANUAL_EXIT</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>SENSEX2691774500CE</t>
+        </is>
+      </c>
+      <c r="E25" t="n">
+        <v>114.2</v>
+      </c>
+      <c r="F25" t="n">
+        <v>40</v>
+      </c>
+      <c r="G25" t="n">
+        <v>4</v>
+      </c>
+      <c r="H25" t="inlineStr"/>
+      <c r="I25" t="inlineStr"/>
+      <c r="J25" t="inlineStr"/>
+      <c r="K25" t="inlineStr"/>
+      <c r="L25" t="inlineStr"/>
+      <c r="M25" t="inlineStr"/>
+      <c r="N25" t="inlineStr"/>
+      <c r="O25" t="inlineStr"/>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>2026-09-17 14:57:29</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>LIVE</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>ENTRY</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>SENSEX2691774500CE</t>
+        </is>
+      </c>
+      <c r="E26" t="n">
+        <v>116.9</v>
+      </c>
+      <c r="F26" t="n">
+        <v>40</v>
+      </c>
+      <c r="G26" t="n">
+        <v>5</v>
+      </c>
+      <c r="H26" t="inlineStr"/>
+      <c r="I26" t="inlineStr"/>
+      <c r="J26" t="inlineStr"/>
+      <c r="K26" t="inlineStr"/>
+      <c r="L26" t="inlineStr"/>
+      <c r="M26" t="inlineStr"/>
+      <c r="N26" t="inlineStr"/>
+      <c r="O26" t="inlineStr"/>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>2026-09-17 14:57:33</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>LIVE</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>MANUAL_EXIT</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>SENSEX2691774500CE</t>
+        </is>
+      </c>
+      <c r="E27" t="n">
+        <v>117.6</v>
+      </c>
+      <c r="F27" t="n">
+        <v>40</v>
+      </c>
+      <c r="G27" t="n">
+        <v>5</v>
+      </c>
+      <c r="H27" t="inlineStr"/>
+      <c r="I27" t="inlineStr"/>
+      <c r="J27" t="inlineStr"/>
+      <c r="K27" t="inlineStr"/>
+      <c r="L27" t="inlineStr"/>
+      <c r="M27" t="inlineStr"/>
+      <c r="N27" t="inlineStr"/>
+      <c r="O27" t="inlineStr"/>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>2026-09-17 14:58:03</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>LIVE</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>ENTRY</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>SENSEX2691774500CE</t>
+        </is>
+      </c>
+      <c r="E28" t="n">
+        <v>117.6</v>
+      </c>
+      <c r="F28" t="n">
+        <v>40</v>
+      </c>
+      <c r="G28" t="n">
+        <v>6</v>
+      </c>
+      <c r="H28" t="inlineStr"/>
+      <c r="I28" t="inlineStr"/>
+      <c r="J28" t="inlineStr"/>
+      <c r="K28" t="inlineStr"/>
+      <c r="L28" t="inlineStr"/>
+      <c r="M28" t="inlineStr"/>
+      <c r="N28" t="inlineStr"/>
+      <c r="O28" t="inlineStr"/>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>2026-09-17 14:58:08</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>LIVE</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>MANUAL_EXIT</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>SENSEX2691774500CE</t>
+        </is>
+      </c>
+      <c r="E29" t="n">
+        <v>114.75</v>
+      </c>
+      <c r="F29" t="n">
+        <v>40</v>
+      </c>
+      <c r="G29" t="n">
+        <v>6</v>
+      </c>
+      <c r="H29" t="inlineStr"/>
+      <c r="I29" t="inlineStr"/>
+      <c r="J29" t="inlineStr"/>
+      <c r="K29" t="inlineStr"/>
+      <c r="L29" t="inlineStr"/>
+      <c r="M29" t="inlineStr"/>
+      <c r="N29" t="inlineStr"/>
+      <c r="O29" t="inlineStr"/>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>2026-09-17 14:58:38</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>LIVE</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>ENTRY</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>SENSEX2691774500CE</t>
+        </is>
+      </c>
+      <c r="E30" t="n">
+        <v>114.75</v>
+      </c>
+      <c r="F30" t="n">
+        <v>40</v>
+      </c>
+      <c r="G30" t="n">
+        <v>7</v>
+      </c>
+      <c r="H30" t="inlineStr"/>
+      <c r="I30" t="inlineStr"/>
+      <c r="J30" t="inlineStr"/>
+      <c r="K30" t="inlineStr"/>
+      <c r="L30" t="inlineStr"/>
+      <c r="M30" t="inlineStr"/>
+      <c r="N30" t="inlineStr"/>
+      <c r="O30" t="inlineStr"/>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>2026-09-17 14:58:42</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>LIVE</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>MANUAL_EXIT</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>SENSEX2691774500CE</t>
+        </is>
+      </c>
+      <c r="E31" t="n">
+        <v>117.35</v>
+      </c>
+      <c r="F31" t="n">
+        <v>40</v>
+      </c>
+      <c r="G31" t="n">
+        <v>7</v>
+      </c>
+      <c r="H31" t="inlineStr"/>
+      <c r="I31" t="inlineStr"/>
+      <c r="J31" t="inlineStr"/>
+      <c r="K31" t="inlineStr"/>
+      <c r="L31" t="inlineStr"/>
+      <c r="M31" t="inlineStr"/>
+      <c r="N31" t="inlineStr"/>
+      <c r="O31" t="inlineStr"/>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>2026-09-17 14:59:11</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>LIVE</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>ENTRY</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>SENSEX2691774500CE</t>
+        </is>
+      </c>
+      <c r="E32" t="n">
+        <v>117.35</v>
+      </c>
+      <c r="F32" t="n">
+        <v>40</v>
+      </c>
+      <c r="G32" t="n">
+        <v>8</v>
+      </c>
+      <c r="H32" t="inlineStr"/>
+      <c r="I32" t="inlineStr"/>
+      <c r="J32" t="inlineStr"/>
+      <c r="K32" t="inlineStr"/>
+      <c r="L32" t="inlineStr"/>
+      <c r="M32" t="inlineStr"/>
+      <c r="N32" t="inlineStr"/>
+      <c r="O32" t="inlineStr"/>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>2026-09-17 14:59:15</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>LIVE</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>MANUAL_EXIT</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>SENSEX2691774500CE</t>
+        </is>
+      </c>
+      <c r="E33" t="n">
+        <v>117.55</v>
+      </c>
+      <c r="F33" t="n">
+        <v>40</v>
+      </c>
+      <c r="G33" t="n">
+        <v>8</v>
+      </c>
+      <c r="H33" t="inlineStr"/>
+      <c r="I33" t="inlineStr"/>
+      <c r="J33" t="inlineStr"/>
+      <c r="K33" t="inlineStr"/>
+      <c r="L33" t="inlineStr"/>
+      <c r="M33" t="inlineStr"/>
+      <c r="N33" t="inlineStr"/>
+      <c r="O33" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/signal_tracker.xlsx
+++ b/signal_tracker.xlsx
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Y10"/>
+  <dimension ref="A1:Y11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1074,6 +1074,61 @@
       <c r="Y10" t="n">
         <v>1</v>
       </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>2026-09-18 13:35:51</t>
+        </is>
+      </c>
+      <c r="B11" t="n">
+        <v>74537.69</v>
+      </c>
+      <c r="C11" t="n">
+        <v>11.53</v>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>SENSEX26SEP74500CE</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>468.9</v>
+      </c>
+      <c r="F11" t="n">
+        <v>390.4681750284118</v>
+      </c>
+      <c r="G11" t="n">
+        <v>547.3318249715882</v>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>SENSEX26SEP74500PE</t>
+        </is>
+      </c>
+      <c r="I11" t="n">
+        <v>375.1</v>
+      </c>
+      <c r="J11" t="n">
+        <v>310.287382322764</v>
+      </c>
+      <c r="K11" t="n">
+        <v>439.912617677236</v>
+      </c>
+      <c r="L11" t="inlineStr"/>
+      <c r="M11" t="inlineStr"/>
+      <c r="N11" t="inlineStr"/>
+      <c r="O11" t="inlineStr"/>
+      <c r="P11" t="inlineStr"/>
+      <c r="Q11" t="inlineStr"/>
+      <c r="R11" t="inlineStr"/>
+      <c r="S11" t="inlineStr"/>
+      <c r="T11" t="inlineStr"/>
+      <c r="U11" t="inlineStr"/>
+      <c r="V11" t="inlineStr"/>
+      <c r="W11" t="inlineStr"/>
+      <c r="X11" t="inlineStr"/>
+      <c r="Y11" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
